--- a/doc/axi4_vip_vplan.xlsx
+++ b/doc/axi4_vip_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi4_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A257D85-B4A5-44E3-A512-61791E52722B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A3B763-4F42-435D-ADA8-2C4299DD517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
   <si>
     <t>Description</t>
   </si>
@@ -34,18 +34,9 @@
     <t>Sequences Used</t>
   </si>
   <si>
-    <t>Seed / Configuration</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -71,6 +62,114 @@
   </si>
   <si>
     <t>Error Injection</t>
+  </si>
+  <si>
+    <t>axi4_wr_rd_test</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>axi4_base_test</t>
+  </si>
+  <si>
+    <t>Base UVM test class setting up the simulation environment configuration, including active agent status, scoreboards, coverage collector, and virtual interface connections.</t>
+  </si>
+  <si>
+    <t>Environment setup &amp; verification topology instantiation.</t>
+  </si>
+  <si>
+    <t>None (Base class)</t>
+  </si>
+  <si>
+    <t>Performs iterative write transactions immediately followed by reads from the identical addresses to check basic functionality.</t>
+  </si>
+  <si>
+    <t>Basic Write/Read transactions, scoreboard matching, memory model data retention.</t>
+  </si>
+  <si>
+    <t>axi4_write_read_back_seq</t>
+  </si>
+  <si>
+    <t>axi4_random_test</t>
+  </si>
+  <si>
+    <t>Initiates fully randomized sequences of mixed write and read transfers to verify VIP behavior under concurrent master/slave traffic conditions.</t>
+  </si>
+  <si>
+    <t>Mixed traffic stress testing, variable delays, default random constraint verification.</t>
+  </si>
+  <si>
+    <t>axi4_random_seq</t>
+  </si>
+  <si>
+    <t>axi4_outstanding_test</t>
+  </si>
+  <si>
+    <t>Simulates concurrent read and write bursts using fork-join threads up to a specified maximum outstanding transaction depth.</t>
+  </si>
+  <si>
+    <t>Multi-outstanding addressing, read/write transaction pipelining, and channel interleaving.</t>
+  </si>
+  <si>
+    <t>axi4_outstanding_seq</t>
+  </si>
+  <si>
+    <t>axi4_exclusive_test</t>
+  </si>
+  <si>
+    <t>Tests AXI4 exclusive access locks. It generates matching exclusive read-write sequences targeting EXOKAY responses, and unmatched writes targeting OKAY response.</t>
+  </si>
+  <si>
+    <t>Atomic operations, exclusive locks, exclusive monitoring tracking in slave model.</t>
+  </si>
+  <si>
+    <t>axi4_exclusive_seq</t>
+  </si>
+  <si>
+    <t>axi4_unaligned_test</t>
+  </si>
+  <si>
+    <t>Sweeps unaligned start addresses relative to transfer size (e.g. 2B or 4B sizes starting at offsets where address modulo size is non-zero).</t>
+  </si>
+  <si>
+    <t>Unaligned transfer addressing, byte-lane strobe logic.</t>
+  </si>
+  <si>
+    <t>axi4_unaligned_seq</t>
+  </si>
+  <si>
+    <t>Validates write strobe pattern variations including full strobes, zero-byte strobes (sparse transfers), and walking-one/halfword patterns.</t>
+  </si>
+  <si>
+    <t>axi4_strobe_test</t>
+  </si>
+  <si>
+    <t>Write strobe masking (wstrb), sparse write handling, and byte-lane data validity.</t>
+  </si>
+  <si>
+    <t>axi4_strobe_pattern_seq</t>
+  </si>
+  <si>
+    <t>axi4_burst_sweep_test</t>
+  </si>
+  <si>
+    <t>Sweeps all valid cross-combinations of burst type (FIXED, INCR, WRAP), transfer size, and burst length. Also tests error injection regions.</t>
+  </si>
+  <si>
+    <t>Cross-coverage of burst attributes, protocol validation, SLVERR/DECERR error injection.</t>
+  </si>
+  <si>
+    <t>axi4_burst_sweep_seq</t>
+  </si>
+  <si>
+    <t>axi4_cache_prot_test</t>
+  </si>
+  <si>
+    <t>Systematically sweeps all 16 values of AXI4 memory cache (cache) attributes and 8 values of protection (prot) attributes for both read and write transactions.</t>
+  </si>
+  <si>
+    <t>Memory attribute constraints, access permission types, cacheability/buffering protocols.</t>
   </si>
 </sst>
 </file>
@@ -385,10 +484,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -652,28 +747,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="51.88671875" style="2" customWidth="1"/>
     <col min="3" max="3" width="30.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="46.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="9" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="20.77734375" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -681,959 +774,825 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
-    </row>
-    <row r="33" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8"/>
-    </row>
-    <row r="34" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
-    </row>
-    <row r="35" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8"/>
-    </row>
-    <row r="36" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="8"/>
+    </row>
+    <row r="36" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="8"/>
-    </row>
-    <row r="37" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="8"/>
+    </row>
+    <row r="37" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="8"/>
-    </row>
-    <row r="38" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="8"/>
+    </row>
+    <row r="38" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="39" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E38" s="8"/>
+    </row>
+    <row r="39" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="8"/>
-    </row>
-    <row r="41" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E40" s="8"/>
+    </row>
+    <row r="41" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="8"/>
-    </row>
-    <row r="42" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E41" s="8"/>
+    </row>
+    <row r="42" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="8"/>
-    </row>
-    <row r="43" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E42" s="8"/>
+    </row>
+    <row r="43" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E43" s="8"/>
+    </row>
+    <row r="44" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="8"/>
-    </row>
-    <row r="45" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E44" s="8"/>
+    </row>
+    <row r="45" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="8"/>
-    </row>
-    <row r="46" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E45" s="8"/>
+    </row>
+    <row r="46" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E46" s="8"/>
+    </row>
+    <row r="47" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="8"/>
-    </row>
-    <row r="48" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E47" s="8"/>
+    </row>
+    <row r="48" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="8"/>
-    </row>
-    <row r="49" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E48" s="8"/>
+    </row>
+    <row r="49" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="8"/>
-    </row>
-    <row r="50" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="8"/>
-    </row>
-    <row r="51" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E50" s="8"/>
+    </row>
+    <row r="51" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="8"/>
-    </row>
-    <row r="52" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="8"/>
-    </row>
-    <row r="53" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E52" s="8"/>
+    </row>
+    <row r="53" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="8"/>
-    </row>
-    <row r="55" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="8"/>
-    </row>
-    <row r="56" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E55" s="8"/>
+    </row>
+    <row r="56" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="8"/>
-    </row>
-    <row r="57" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="8"/>
-    </row>
-    <row r="58" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="8"/>
-    </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="8"/>
+    </row>
+    <row r="59" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="8"/>
-    </row>
-    <row r="60" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E59" s="8"/>
+    </row>
+    <row r="60" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="8"/>
-    </row>
-    <row r="61" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E60" s="8"/>
+    </row>
+    <row r="61" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="8"/>
-    </row>
-    <row r="62" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E61" s="8"/>
+    </row>
+    <row r="62" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="8"/>
-    </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E62" s="8"/>
+    </row>
+    <row r="63" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="8"/>
-    </row>
-    <row r="64" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E63" s="8"/>
+    </row>
+    <row r="64" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="8"/>
-    </row>
-    <row r="65" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E64" s="8"/>
+    </row>
+    <row r="65" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="8"/>
-    </row>
-    <row r="66" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E65" s="8"/>
+    </row>
+    <row r="66" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="8"/>
-    </row>
-    <row r="67" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E66" s="8"/>
+    </row>
+    <row r="67" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="8"/>
-    </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E67" s="8"/>
+    </row>
+    <row r="68" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="8"/>
-    </row>
-    <row r="69" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E68" s="8"/>
+    </row>
+    <row r="69" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="8"/>
-    </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E69" s="8"/>
+    </row>
+    <row r="70" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-    </row>
-    <row r="71" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E70" s="8"/>
+    </row>
+    <row r="71" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="8"/>
-    </row>
-    <row r="72" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E71" s="8"/>
+    </row>
+    <row r="72" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="8"/>
-    </row>
-    <row r="73" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E72" s="8"/>
+    </row>
+    <row r="73" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="8"/>
-    </row>
-    <row r="74" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E73" s="8"/>
+    </row>
+    <row r="74" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="8"/>
-    </row>
-    <row r="75" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E74" s="8"/>
+    </row>
+    <row r="75" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="8"/>
-    </row>
-    <row r="76" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E75" s="8"/>
+    </row>
+    <row r="76" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="8"/>
-    </row>
-    <row r="77" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="8"/>
+    </row>
+    <row r="77" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="8"/>
-    </row>
-    <row r="78" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E77" s="8"/>
+    </row>
+    <row r="78" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="8"/>
-    </row>
-    <row r="79" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E78" s="8"/>
+    </row>
+    <row r="79" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="8"/>
-    </row>
-    <row r="80" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E79" s="8"/>
+    </row>
+    <row r="80" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="8"/>
-    </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E80" s="8"/>
+    </row>
+    <row r="81" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="8"/>
-    </row>
-    <row r="82" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E81" s="8"/>
+    </row>
+    <row r="82" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="8"/>
-    </row>
-    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E82" s="8"/>
+    </row>
+    <row r="83" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="8"/>
-    </row>
-    <row r="84" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="8"/>
+    </row>
+    <row r="84" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="8"/>
-    </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="8"/>
+    </row>
+    <row r="85" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="8"/>
-    </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E85" s="8"/>
+    </row>
+    <row r="86" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="8"/>
-    </row>
-    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="8"/>
+    </row>
+    <row r="87" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="8"/>
-    </row>
-    <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="8"/>
+    </row>
+    <row r="88" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="8"/>
-    </row>
-    <row r="89" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E88" s="8"/>
+    </row>
+    <row r="89" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="8"/>
-    </row>
-    <row r="90" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E89" s="8"/>
+    </row>
+    <row r="90" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="8"/>
-    </row>
-    <row r="91" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E90" s="8"/>
+    </row>
+    <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="8"/>
-    </row>
-    <row r="92" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E91" s="8"/>
+    </row>
+    <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="8"/>
-    </row>
-    <row r="93" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E92" s="8"/>
+    </row>
+    <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="8"/>
-    </row>
-    <row r="94" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E93" s="8"/>
+    </row>
+    <row r="94" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="8"/>
-    </row>
-    <row r="95" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E94" s="8"/>
+    </row>
+    <row r="95" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="8"/>
-    </row>
-    <row r="96" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E95" s="8"/>
+    </row>
+    <row r="96" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="8"/>
-    </row>
-    <row r="97" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="8"/>
+    </row>
+    <row r="97" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="8"/>
-    </row>
-    <row r="98" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E97" s="8"/>
+    </row>
+    <row r="98" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="8"/>
-    </row>
-    <row r="99" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E98" s="8"/>
+    </row>
+    <row r="99" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="8"/>
-    </row>
-    <row r="100" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E99" s="8"/>
+    </row>
+    <row r="100" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="7"/>
-      <c r="G100" s="8"/>
+      <c r="E100" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G100">
+  <conditionalFormatting sqref="E2:E100">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Passed",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="Failed">
-      <formula>NOT(ISERROR(SEARCH("Failed",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Failed",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("In Progress",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Not Started">
-      <formula>NOT(ISERROR(SEARCH("Not Started",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Not Started",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="Blocked">
-      <formula>NOT(ISERROR(SEARCH("Blocked",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Blocked",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Passed">
-      <formula>NOT(ISERROR(SEARCH("Passed",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Passed",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="Failed">
-      <formula>NOT(ISERROR(SEARCH("Failed",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Failed",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("In Progress",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="Not Started">
-      <formula>NOT(ISERROR(SEARCH("Not Started",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Not Started",E2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="Blocked">
-      <formula>NOT(ISERROR(SEARCH("Blocked",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Blocked",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G100" xr:uid="{A59F3891-7277-4EB0-B6D5-C873B1C10ABC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{A59F3891-7277-4EB0-B6D5-C873B1C10ABC}">
       <formula1>"Not Started,In Progress,Passed,Failed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1655,36 +1614,36 @@
     <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -1695,7 +1654,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="11"/>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -1706,7 +1665,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1717,7 +1676,7 @@
       <c r="H4" s="12"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -1728,7 +1687,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1739,7 +1698,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1750,7 +1709,7 @@
       <c r="H7" s="6"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1761,7 +1720,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1772,7 +1731,7 @@
       <c r="H9" s="6"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1783,7 +1742,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1794,7 +1753,7 @@
       <c r="H11" s="6"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1805,7 +1764,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1816,7 +1775,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1827,7 +1786,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1838,7 +1797,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1849,7 +1808,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -1860,7 +1819,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1871,7 +1830,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1882,7 +1841,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1893,7 +1852,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1904,7 +1863,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1915,7 +1874,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -1926,7 +1885,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1937,7 +1896,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1948,7 +1907,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -1959,7 +1918,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1970,7 +1929,7 @@
       <c r="H27" s="6"/>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1981,7 +1940,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1992,7 +1951,7 @@
       <c r="H29" s="6"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -2003,7 +1962,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2014,7 +1973,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2025,7 +1984,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -2036,7 +1995,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -2047,7 +2006,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2058,7 +2017,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2069,7 +2028,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -2080,7 +2039,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="7"/>
     </row>
-    <row r="38" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -2091,7 +2050,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2102,7 +2061,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -2113,7 +2072,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="41" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -2124,7 +2083,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="7"/>
     </row>
-    <row r="42" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2135,7 +2094,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -2146,7 +2105,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -2157,7 +2116,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2168,7 +2127,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2179,7 +2138,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2190,7 +2149,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -2201,7 +2160,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="7"/>
     </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -2212,7 +2171,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="7"/>
     </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -2223,7 +2182,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -2234,7 +2193,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -2245,7 +2204,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -2256,7 +2215,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -2267,7 +2226,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2278,7 +2237,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -2289,7 +2248,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2300,7 +2259,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -2311,7 +2270,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -2322,7 +2281,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -2333,7 +2292,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="7"/>
     </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -2344,7 +2303,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="7"/>
     </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -2355,7 +2314,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -2366,7 +2325,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="7"/>
     </row>
-    <row r="64" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -2377,7 +2336,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -2388,7 +2347,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="7"/>
     </row>
-    <row r="66" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -2399,7 +2358,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -2410,7 +2369,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -2421,7 +2380,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2432,7 +2391,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="7"/>
     </row>
-    <row r="70" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -2443,7 +2402,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="7"/>
     </row>
-    <row r="71" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -2454,7 +2413,7 @@
       <c r="H71" s="8"/>
       <c r="I71" s="7"/>
     </row>
-    <row r="72" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -2465,7 +2424,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="7"/>
     </row>
-    <row r="73" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -2476,7 +2435,7 @@
       <c r="H73" s="8"/>
       <c r="I73" s="7"/>
     </row>
-    <row r="74" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -2487,7 +2446,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="7"/>
     </row>
-    <row r="75" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -2498,7 +2457,7 @@
       <c r="H75" s="8"/>
       <c r="I75" s="7"/>
     </row>
-    <row r="76" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -2509,7 +2468,7 @@
       <c r="H76" s="8"/>
       <c r="I76" s="7"/>
     </row>
-    <row r="77" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -2520,7 +2479,7 @@
       <c r="H77" s="8"/>
       <c r="I77" s="7"/>
     </row>
-    <row r="78" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -2531,7 +2490,7 @@
       <c r="H78" s="8"/>
       <c r="I78" s="7"/>
     </row>
-    <row r="79" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -2542,7 +2501,7 @@
       <c r="H79" s="8"/>
       <c r="I79" s="7"/>
     </row>
-    <row r="80" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -2553,7 +2512,7 @@
       <c r="H80" s="8"/>
       <c r="I80" s="7"/>
     </row>
-    <row r="81" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -2564,7 +2523,7 @@
       <c r="H81" s="8"/>
       <c r="I81" s="7"/>
     </row>
-    <row r="82" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -2575,7 +2534,7 @@
       <c r="H82" s="8"/>
       <c r="I82" s="7"/>
     </row>
-    <row r="83" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -2586,7 +2545,7 @@
       <c r="H83" s="8"/>
       <c r="I83" s="7"/>
     </row>
-    <row r="84" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -2597,7 +2556,7 @@
       <c r="H84" s="8"/>
       <c r="I84" s="7"/>
     </row>
-    <row r="85" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -2608,7 +2567,7 @@
       <c r="H85" s="8"/>
       <c r="I85" s="7"/>
     </row>
-    <row r="86" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -2619,7 +2578,7 @@
       <c r="H86" s="8"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -2630,7 +2589,7 @@
       <c r="H87" s="8"/>
       <c r="I87" s="7"/>
     </row>
-    <row r="88" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -2641,7 +2600,7 @@
       <c r="H88" s="8"/>
       <c r="I88" s="7"/>
     </row>
-    <row r="89" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -2652,7 +2611,7 @@
       <c r="H89" s="8"/>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -2663,7 +2622,7 @@
       <c r="H90" s="8"/>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -2674,7 +2633,7 @@
       <c r="H91" s="8"/>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -2685,7 +2644,7 @@
       <c r="H92" s="8"/>
       <c r="I92" s="7"/>
     </row>
-    <row r="93" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -2696,7 +2655,7 @@
       <c r="H93" s="8"/>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -2707,7 +2666,7 @@
       <c r="H94" s="8"/>
       <c r="I94" s="7"/>
     </row>
-    <row r="95" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -2718,7 +2677,7 @@
       <c r="H95" s="8"/>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -2729,7 +2688,7 @@
       <c r="H96" s="8"/>
       <c r="I96" s="7"/>
     </row>
-    <row r="97" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -2740,7 +2699,7 @@
       <c r="H97" s="8"/>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -2751,7 +2710,7 @@
       <c r="H98" s="8"/>
       <c r="I98" s="7"/>
     </row>
-    <row r="99" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -2762,7 +2721,7 @@
       <c r="H99" s="8"/>
       <c r="I99" s="7"/>
     </row>
-    <row r="100" spans="1:9" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -2778,23 +2737,15 @@
     <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="None">
       <formula>NOT(ISERROR(SEARCH("None",H2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H100">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="SLVERR">
       <formula>NOT(ISERROR(SEARCH("SLVERR",H2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H100">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="DECERR">
       <formula>NOT(ISERROR(SEARCH("DECERR",H2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H100">
     <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Protocol Violation">
       <formula>NOT(ISERROR(SEARCH("Protocol Violation",H2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H100">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Timeout">
       <formula>NOT(ISERROR(SEARCH("Timeout",H2)))</formula>
     </cfRule>

--- a/doc/axi4_vip_vplan.xlsx
+++ b/doc/axi4_vip_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi4_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A3B763-4F42-435D-ADA8-2C4299DD517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296795B2-C578-4875-9C34-4D45BB1FE2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>Description</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>In Progress</t>
+  </si>
+  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -121,18 +124,12 @@
     <t>Tests AXI4 exclusive access locks. It generates matching exclusive read-write sequences targeting EXOKAY responses, and unmatched writes targeting OKAY response.</t>
   </si>
   <si>
-    <t>Atomic operations, exclusive locks, exclusive monitoring tracking in slave model.</t>
-  </si>
-  <si>
     <t>axi4_exclusive_seq</t>
   </si>
   <si>
     <t>axi4_unaligned_test</t>
   </si>
   <si>
-    <t>Sweeps unaligned start addresses relative to transfer size (e.g. 2B or 4B sizes starting at offsets where address modulo size is non-zero).</t>
-  </si>
-  <si>
     <t>Unaligned transfer addressing, byte-lane strobe logic.</t>
   </si>
   <si>
@@ -170,6 +167,12 @@
   </si>
   <si>
     <t>Memory attribute constraints, access permission types, cacheability/buffering protocols.</t>
+  </si>
+  <si>
+    <t>Sweeps unaligned start addresses relative to transfer size.</t>
+  </si>
+  <si>
+    <t>Exclusive access in slave model.</t>
   </si>
 </sst>
 </file>
@@ -750,23 +753,23 @@
   <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="51.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="80.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="40.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.77734375" style="9" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -777,87 +780,87 @@
     </row>
     <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -865,67 +868,67 @@
         <v>33</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -1616,28 +1619,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I1" s="10" t="s">
         <v>0</v>

--- a/doc/axi4_vip_vplan.xlsx
+++ b/doc/axi4_vip_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi4_vip\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296795B2-C578-4875-9C34-4D45BB1FE2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAEBCFA-FE47-4ECC-BCBB-391B65F9A121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>Description</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
@@ -49,9 +46,6 @@
     <t>Sequence</t>
   </si>
   <si>
-    <t>Channel Focus</t>
-  </si>
-  <si>
     <t>Burst Type (AxBURST)</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>Error Injection</t>
   </si>
   <si>
-    <t>axi4_wr_rd_test</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
@@ -79,100 +70,115 @@
     <t>Base UVM test class setting up the simulation environment configuration, including active agent status, scoreboards, coverage collector, and virtual interface connections.</t>
   </si>
   <si>
-    <t>Environment setup &amp; verification topology instantiation.</t>
-  </si>
-  <si>
     <t>None (Base class)</t>
   </si>
   <si>
-    <t>Performs iterative write transactions immediately followed by reads from the identical addresses to check basic functionality.</t>
-  </si>
-  <si>
-    <t>Basic Write/Read transactions, scoreboard matching, memory model data retention.</t>
-  </si>
-  <si>
     <t>axi4_write_read_back_seq</t>
   </si>
   <si>
     <t>axi4_random_test</t>
   </si>
   <si>
-    <t>Initiates fully randomized sequences of mixed write and read transfers to verify VIP behavior under concurrent master/slave traffic conditions.</t>
-  </si>
-  <si>
-    <t>Mixed traffic stress testing, variable delays, default random constraint verification.</t>
-  </si>
-  <si>
     <t>axi4_random_seq</t>
   </si>
   <si>
     <t>axi4_outstanding_test</t>
   </si>
   <si>
-    <t>Simulates concurrent read and write bursts using fork-join threads up to a specified maximum outstanding transaction depth.</t>
-  </si>
-  <si>
-    <t>Multi-outstanding addressing, read/write transaction pipelining, and channel interleaving.</t>
-  </si>
-  <si>
     <t>axi4_outstanding_seq</t>
   </si>
   <si>
     <t>axi4_exclusive_test</t>
   </si>
   <si>
-    <t>Tests AXI4 exclusive access locks. It generates matching exclusive read-write sequences targeting EXOKAY responses, and unmatched writes targeting OKAY response.</t>
-  </si>
-  <si>
     <t>axi4_exclusive_seq</t>
   </si>
   <si>
     <t>axi4_unaligned_test</t>
   </si>
   <si>
-    <t>Unaligned transfer addressing, byte-lane strobe logic.</t>
-  </si>
-  <si>
     <t>axi4_unaligned_seq</t>
   </si>
   <si>
-    <t>Validates write strobe pattern variations including full strobes, zero-byte strobes (sparse transfers), and walking-one/halfword patterns.</t>
-  </si>
-  <si>
     <t>axi4_strobe_test</t>
   </si>
   <si>
-    <t>Write strobe masking (wstrb), sparse write handling, and byte-lane data validity.</t>
-  </si>
-  <si>
     <t>axi4_strobe_pattern_seq</t>
   </si>
   <si>
     <t>axi4_burst_sweep_test</t>
   </si>
   <si>
-    <t>Sweeps all valid cross-combinations of burst type (FIXED, INCR, WRAP), transfer size, and burst length. Also tests error injection regions.</t>
-  </si>
-  <si>
-    <t>Cross-coverage of burst attributes, protocol validation, SLVERR/DECERR error injection.</t>
-  </si>
-  <si>
     <t>axi4_burst_sweep_seq</t>
   </si>
   <si>
     <t>axi4_cache_prot_test</t>
   </si>
   <si>
-    <t>Systematically sweeps all 16 values of AXI4 memory cache (cache) attributes and 8 values of protection (prot) attributes for both read and write transactions.</t>
-  </si>
-  <si>
-    <t>Memory attribute constraints, access permission types, cacheability/buffering protocols.</t>
-  </si>
-  <si>
-    <t>Sweeps unaligned start addresses relative to transfer size.</t>
-  </si>
-  <si>
-    <t>Exclusive access in slave model.</t>
+    <t>axi4_sanity_test</t>
+  </si>
+  <si>
+    <t>Performs basic back-to-back write and read-back operations on random addresses to verify basic connectivity and scoreboard accuracy.</t>
+  </si>
+  <si>
+    <t>VIP Environment Setup &amp; Base Configuration</t>
+  </si>
+  <si>
+    <t>Basic Write/Read Transactions &amp; Scoreboard</t>
+  </si>
+  <si>
+    <t>Iterates through combinations of burst types (FIXED, INCR, WRAP) and sizes to verify compliance with burst protocol rules.</t>
+  </si>
+  <si>
+    <t>Burst Modes &amp; Transfer Size Compliance</t>
+  </si>
+  <si>
+    <t>Sweeps different combinations of cache (axcache) and protection (axprot) attributes to verify memory properties and secure access mechanisms.</t>
+  </si>
+  <si>
+    <t>axi4_cache_prot_seq</t>
+  </si>
+  <si>
+    <t>Executes exclusive access transactions using axlock to verify semaphore lock state tracking and EXOKAY response generation at the slave side.</t>
+  </si>
+  <si>
+    <t>Exclusive Access Locks &amp; Semaphore Mechanisms</t>
+  </si>
+  <si>
+    <t>Generates concurrent read and write transactions up to the maximum configured depth to stress-test pipeline queuing and tracking.</t>
+  </si>
+  <si>
+    <t>Outstanding Transactions &amp; Pipeline Stress-testing</t>
+  </si>
+  <si>
+    <t>axi4_out_of_order_test</t>
+  </si>
+  <si>
+    <t>Drives concurrent outstanding transactions with multiple IDs and checks the VIP's capability to process and match out-of-order responses.</t>
+  </si>
+  <si>
+    <t>axi4_out_of_order_seq</t>
+  </si>
+  <si>
+    <t>Out-of-Order Multi-ID Responses</t>
+  </si>
+  <si>
+    <t>Mixed Random Bus Traffic</t>
+  </si>
+  <si>
+    <t>Asserts various write strobe (wstrb) patterns (full, sparse, partial) to ensure correct byte-level updates in the slave memory model.</t>
+  </si>
+  <si>
+    <t>Write Strobe (Byte-Enables) Validation</t>
+  </si>
+  <si>
+    <t>Executes read and write transfers starting at unaligned addresses to verify address calculation and data alignment logic.</t>
+  </si>
+  <si>
+    <t>Unaligned Address/Data Transfers</t>
+  </si>
+  <si>
+    <t>Generates fully randomized mixed read and write traffic to simulate realistic bus activity and stress-test the environment.</t>
   </si>
 </sst>
 </file>
@@ -487,6 +493,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -763,13 +773,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -780,163 +790,173 @@
     </row>
     <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
@@ -1595,7 +1615,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E100" xr:uid="{A59F3891-7277-4EB0-B6D5-C873B1C10ABC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E100 E2:E11" xr:uid="{A59F3891-7277-4EB0-B6D5-C873B1C10ABC}">
       <formula1>"Not Started,In Progress,Passed,Failed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1606,1155 +1626,1053 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5492F47D-205A-4E23-8817-679E768748AA}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.77734375" style="2" customWidth="1"/>
-    <col min="2" max="5" width="30.77734375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="30.77734375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="30.77734375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="50.77734375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="2" max="4" width="30.77734375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="30.77734375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="50.77734375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="H1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="11"/>
-    </row>
-    <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
       <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
       <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="12"/>
       <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="11"/>
-    </row>
-    <row r="29" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="12"/>
       <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8"/>
       <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8"/>
       <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="7"/>
-    </row>
-    <row r="42" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="7"/>
-    </row>
-    <row r="43" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="7"/>
-    </row>
-    <row r="44" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="7"/>
-    </row>
-    <row r="45" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="7"/>
-    </row>
-    <row r="46" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="7"/>
-    </row>
-    <row r="47" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="7"/>
-    </row>
-    <row r="48" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="7"/>
-    </row>
-    <row r="50" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="7"/>
-    </row>
-    <row r="52" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="7"/>
-    </row>
-    <row r="53" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="7"/>
-    </row>
-    <row r="54" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="7"/>
+    </row>
+    <row r="54" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="8"/>
       <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="7"/>
-    </row>
-    <row r="57" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="8"/>
       <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="7"/>
-    </row>
-    <row r="58" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="7"/>
-    </row>
-    <row r="59" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="7"/>
+    </row>
+    <row r="59" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8"/>
       <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="60" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="7"/>
+    </row>
+    <row r="60" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="7"/>
-    </row>
-    <row r="61" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8"/>
       <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="7"/>
-    </row>
-    <row r="62" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="7"/>
-    </row>
-    <row r="63" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8"/>
       <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="7"/>
-    </row>
-    <row r="64" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="7"/>
+    </row>
+    <row r="64" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="7"/>
-    </row>
-    <row r="65" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="7"/>
+    </row>
+    <row r="65" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="8"/>
       <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="7"/>
-    </row>
-    <row r="66" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="7"/>
+    </row>
+    <row r="66" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="7"/>
-    </row>
-    <row r="67" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="7"/>
+    </row>
+    <row r="67" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="8"/>
       <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="7"/>
-    </row>
-    <row r="68" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H67" s="7"/>
+    </row>
+    <row r="68" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="7"/>
-    </row>
-    <row r="69" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H68" s="7"/>
+    </row>
+    <row r="69" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8"/>
       <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="7"/>
-    </row>
-    <row r="70" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="7"/>
-    </row>
-    <row r="71" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="7"/>
+    </row>
+    <row r="71" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8"/>
       <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="7"/>
-    </row>
-    <row r="72" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="7"/>
+    </row>
+    <row r="72" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="7"/>
-    </row>
-    <row r="73" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="7"/>
+    </row>
+    <row r="73" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="8"/>
       <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="7"/>
-    </row>
-    <row r="74" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="7"/>
+    </row>
+    <row r="74" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="7"/>
-    </row>
-    <row r="75" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="8"/>
       <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="7"/>
-    </row>
-    <row r="76" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="7"/>
+    </row>
+    <row r="76" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="7"/>
-    </row>
-    <row r="77" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="8"/>
       <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="7"/>
-    </row>
-    <row r="78" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="7"/>
+    </row>
+    <row r="78" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="8"/>
       <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="7"/>
-    </row>
-    <row r="79" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="7"/>
+    </row>
+    <row r="79" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="8"/>
       <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="7"/>
-    </row>
-    <row r="80" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="7"/>
+    </row>
+    <row r="80" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="8"/>
       <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="7"/>
-    </row>
-    <row r="81" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H80" s="7"/>
+    </row>
+    <row r="81" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="8"/>
       <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="7"/>
-    </row>
-    <row r="82" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="7"/>
+    </row>
+    <row r="82" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="8"/>
       <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="7"/>
-    </row>
-    <row r="83" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H82" s="7"/>
+    </row>
+    <row r="83" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="8"/>
       <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="7"/>
-    </row>
-    <row r="84" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="7"/>
+    </row>
+    <row r="84" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="8"/>
       <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="7"/>
-    </row>
-    <row r="85" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="7"/>
+    </row>
+    <row r="85" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="8"/>
       <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="7"/>
-    </row>
-    <row r="86" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="7"/>
+    </row>
+    <row r="86" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="8"/>
       <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="7"/>
-    </row>
-    <row r="87" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="7"/>
+    </row>
+    <row r="87" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="8"/>
       <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="7"/>
-    </row>
-    <row r="88" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="7"/>
+    </row>
+    <row r="88" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="8"/>
       <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="7"/>
-    </row>
-    <row r="89" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H88" s="7"/>
+    </row>
+    <row r="89" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="8"/>
       <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="7"/>
-    </row>
-    <row r="90" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="7"/>
+    </row>
+    <row r="90" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="8"/>
       <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="7"/>
-    </row>
-    <row r="91" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="7"/>
+    </row>
+    <row r="91" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="8"/>
       <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="7"/>
-    </row>
-    <row r="92" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="8"/>
       <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="7"/>
-    </row>
-    <row r="93" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="7"/>
+    </row>
+    <row r="93" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="8"/>
       <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="7"/>
-    </row>
-    <row r="94" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="8"/>
       <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="7"/>
-    </row>
-    <row r="95" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H94" s="7"/>
+    </row>
+    <row r="95" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="8"/>
       <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="7"/>
-    </row>
-    <row r="96" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H95" s="7"/>
+    </row>
+    <row r="96" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="8"/>
       <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="7"/>
-    </row>
-    <row r="97" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="7"/>
+    </row>
+    <row r="97" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="8"/>
       <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="7"/>
-    </row>
-    <row r="98" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="8"/>
       <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="7"/>
-    </row>
-    <row r="99" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="8"/>
       <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="7"/>
-    </row>
-    <row r="100" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H99" s="7"/>
+    </row>
+    <row r="100" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="8"/>
       <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="7"/>
+      <c r="H100" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H100">
+  <conditionalFormatting sqref="G2:G100">
     <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="None">
-      <formula>NOT(ISERROR(SEARCH("None",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("None",G2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="SLVERR">
-      <formula>NOT(ISERROR(SEARCH("SLVERR",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SLVERR",G2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="DECERR">
-      <formula>NOT(ISERROR(SEARCH("DECERR",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("DECERR",G2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Protocol Violation">
-      <formula>NOT(ISERROR(SEARCH("Protocol Violation",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Protocol Violation",G2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Timeout">
-      <formula>NOT(ISERROR(SEARCH("Timeout",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Timeout",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C100" xr:uid="{A89AB7D5-EA65-481F-8282-9B1EE240D171}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B100" xr:uid="{A89AB7D5-EA65-481F-8282-9B1EE240D171}">
       <formula1>"FIXED (00),INCR (01),WRAP (10),Reserved (11)"</formula1>
     </dataValidation>
   </dataValidations>
